--- a/cloudflare-deploy/public/library/teacher/teacher-en.xlsx
+++ b/cloudflare-deploy/public/library/teacher/teacher-en.xlsx
@@ -1205,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1921,6 +1921,33 @@
       <c r="E28" s="15" t="inlineStr">
         <is>
           <t>Listen slowly and repeat clearly to nail the four tones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>🤖</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>AI Coaching After Class</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>End the video class with ‘Leave’ and the coaching card appears automatically. → Toggle 🇰🇷 Korean / 🇺🇸 English to read it in the language you prefer. → Check the engagement · talk-ratio · praise-count summary and the strengths · improvements · one action. → Press ‘Full report’ to see class details plus recent coaching history (quality score · summary).</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>Trying just the ‘one action for today’ in your next class visibly improves how you draw out student speech.</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F289"/>
+  <dimension ref="A1:F302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5126,8 +5153,156 @@
       <c r="E289" s="33" t="n"/>
       <c r="F289" s="33" t="n"/>
     </row>
+    <row r="291" ht="26" customHeight="1">
+      <c r="A291" s="21" t="inlineStr">
+        <is>
+          <t>26  🤖 AI Coaching After Class  —  Strengths · areas to improve · one action for today</t>
+        </is>
+      </c>
+      <c r="B291" s="22" t="n"/>
+      <c r="C291" s="22" t="n"/>
+      <c r="D291" s="22" t="n"/>
+      <c r="E291" s="22" t="n"/>
+      <c r="F291" s="22" t="n"/>
+    </row>
+    <row r="292" ht="42" customHeight="1">
+      <c r="A292" s="23" t="inlineStr">
+        <is>
+          <t>📖 When you finish and leave a class, the AI analyzes it and shows a coaching card with ‘What you did well / Areas to improve / One action for today’ in both Korean and English. Based on real class signals — talk ratio, engagement, praise count — it helps in a warm coaching tone, not surveillance.</t>
+        </is>
+      </c>
+      <c r="B292" s="24" t="n"/>
+      <c r="C292" s="24" t="n"/>
+      <c r="D292" s="24" t="n"/>
+      <c r="E292" s="24" t="n"/>
+      <c r="F292" s="24" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B293" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="30" customHeight="1">
+      <c r="A294" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B294" s="28" t="inlineStr">
+        <is>
+          <t>End the video class with ‘Leave’ and the coaching card appears automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="30" customHeight="1">
+      <c r="A295" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B295" s="28" t="inlineStr">
+        <is>
+          <t>Toggle 🇰🇷 Korean / 🇺🇸 English to read it in the language you prefer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="30" customHeight="1">
+      <c r="A296" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B296" s="28" t="inlineStr">
+        <is>
+          <t>Check the engagement · talk-ratio · praise-count summary and the strengths · improvements · one action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="30" customHeight="1">
+      <c r="A297" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B297" s="28" t="inlineStr">
+        <is>
+          <t>Press ‘Full report’ to see class details plus recent coaching history (quality score · summary).</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="24" customHeight="1">
+      <c r="A298" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B298" s="30" t="inlineStr">
+        <is>
+          <t>English is the default for native-speaker teachers, with Korean provided alongside.</t>
+        </is>
+      </c>
+      <c r="C298" s="31" t="n"/>
+      <c r="D298" s="31" t="n"/>
+      <c r="E298" s="31" t="n"/>
+      <c r="F298" s="31" t="n"/>
+    </row>
+    <row r="299" ht="24" customHeight="1">
+      <c r="A299" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B299" s="30" t="inlineStr">
+        <is>
+          <t>A class-quality score (0–100) and a detailed summary help you find your own growth points.</t>
+        </is>
+      </c>
+      <c r="C299" s="31" t="n"/>
+      <c r="D299" s="31" t="n"/>
+      <c r="E299" s="31" t="n"/>
+      <c r="F299" s="31" t="n"/>
+    </row>
+    <row r="300" ht="24" customHeight="1">
+      <c r="A300" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B300" s="30" t="inlineStr">
+        <is>
+          <t>Even if the AI is briefly slow, baseline coaching in both languages is always provided.</t>
+        </is>
+      </c>
+      <c r="C300" s="31" t="n"/>
+      <c r="D300" s="31" t="n"/>
+      <c r="E300" s="31" t="n"/>
+      <c r="F300" s="31" t="n"/>
+    </row>
+    <row r="301" ht="26" customHeight="1">
+      <c r="A301" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · Coaching is meant to support your own growth. Admins only receive a monthly rollup.</t>
+        </is>
+      </c>
+      <c r="B301" s="35" t="n"/>
+      <c r="C301" s="35" t="n"/>
+      <c r="D301" s="35" t="n"/>
+      <c r="E301" s="35" t="n"/>
+      <c r="F301" s="35" t="n"/>
+    </row>
+    <row r="302" ht="30" customHeight="1">
+      <c r="A302" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Trying just the ‘one action for today’ in your next class visibly improves how you draw out student speech.</t>
+        </is>
+      </c>
+      <c r="B302" s="33" t="n"/>
+      <c r="C302" s="33" t="n"/>
+      <c r="D302" s="33" t="n"/>
+      <c r="E302" s="33" t="n"/>
+      <c r="F302" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="264">
+  <mergeCells count="276">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="A66:F66"/>
@@ -5150,6 +5325,8 @@
     <mergeCell ref="A239:F239"/>
     <mergeCell ref="B223:F223"/>
     <mergeCell ref="B276:F276"/>
+    <mergeCell ref="B294:F294"/>
+    <mergeCell ref="A301:F301"/>
     <mergeCell ref="B195:F195"/>
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="A150:F150"/>
@@ -5189,6 +5366,7 @@
     <mergeCell ref="A260:F260"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B281:F281"/>
+    <mergeCell ref="A291:F291"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B133:F133"/>
@@ -5208,6 +5386,7 @@
     <mergeCell ref="A277:F277"/>
     <mergeCell ref="B224:F224"/>
     <mergeCell ref="B54:F54"/>
+    <mergeCell ref="A292:F292"/>
     <mergeCell ref="B125:F125"/>
     <mergeCell ref="B72:F72"/>
     <mergeCell ref="B185:F185"/>
@@ -5223,6 +5402,7 @@
     <mergeCell ref="A269:F269"/>
     <mergeCell ref="A151:F151"/>
     <mergeCell ref="B111:F111"/>
+    <mergeCell ref="B293:F293"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="A126:F126"/>
     <mergeCell ref="B98:F98"/>
@@ -5244,6 +5424,7 @@
     <mergeCell ref="B146:F146"/>
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="A176:F176"/>
+    <mergeCell ref="B295:F295"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="B74:F74"/>
     <mergeCell ref="B68:F68"/>
@@ -5260,6 +5441,7 @@
     <mergeCell ref="B216:F216"/>
     <mergeCell ref="B85:F85"/>
     <mergeCell ref="A162:F162"/>
+    <mergeCell ref="B296:F296"/>
     <mergeCell ref="B173:F173"/>
     <mergeCell ref="A227:F227"/>
     <mergeCell ref="B271:F271"/>
@@ -5305,6 +5487,7 @@
     <mergeCell ref="A180:F180"/>
     <mergeCell ref="B225:F225"/>
     <mergeCell ref="B274:F274"/>
+    <mergeCell ref="B299:F299"/>
     <mergeCell ref="A63:F63"/>
     <mergeCell ref="B73:F73"/>
     <mergeCell ref="B191:F191"/>
@@ -5318,6 +5501,7 @@
     <mergeCell ref="B226:F226"/>
     <mergeCell ref="A270:F270"/>
     <mergeCell ref="A279:F279"/>
+    <mergeCell ref="B300:F300"/>
     <mergeCell ref="B183:F183"/>
     <mergeCell ref="A49:F49"/>
     <mergeCell ref="B192:F192"/>
@@ -5350,11 +5534,13 @@
     <mergeCell ref="B102:F102"/>
     <mergeCell ref="A104:F104"/>
     <mergeCell ref="B130:F130"/>
+    <mergeCell ref="A302:F302"/>
     <mergeCell ref="A247:F247"/>
     <mergeCell ref="B86:F86"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="B262:F262"/>
     <mergeCell ref="A219:F219"/>
+    <mergeCell ref="B297:F297"/>
     <mergeCell ref="B235:F235"/>
     <mergeCell ref="A106:F106"/>
     <mergeCell ref="B67:F67"/>
@@ -5375,6 +5561,7 @@
     <mergeCell ref="B283:F283"/>
     <mergeCell ref="A220:F220"/>
     <mergeCell ref="B246:F246"/>
+    <mergeCell ref="B298:F298"/>
     <mergeCell ref="B211:F211"/>
     <mergeCell ref="A148:F148"/>
     <mergeCell ref="B285:F285"/>

--- a/cloudflare-deploy/public/library/teacher/teacher-en.xlsx
+++ b/cloudflare-deploy/public/library/teacher/teacher-en.xlsx
@@ -1108,7 +1108,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>🌐 test.mangoi.co.kr    📞 1588-0000    ✉ support@mangoi.co.kr</t>
+          <t>🌐 www.mangoi.co.kr    📞 1644-0561    ✉ support@mangoi.co.kr</t>
         </is>
       </c>
     </row>

--- a/cloudflare-deploy/public/library/teacher/teacher-en.xlsx
+++ b/cloudflare-deploy/public/library/teacher/teacher-en.xlsx
@@ -1205,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1948,6 +1948,114 @@
       <c r="E29" s="20" t="inlineStr">
         <is>
           <t>Trying just the ‘one action for today’ in your next class visibly improves how you draw out student speech.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Tab Sync (Your Screen Leads)</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>Switch the top tabs as usual (Board · Video · Games · Background · AI Warm-up · Review Quiz). → Watch the student's screen switch to the same tab automatically. → Textbook and file sharing carry over to students the same way.</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>A quick heads-up before jumping to a video or quiz keeps students from being startled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="54" customHeight="1">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>💬</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>1:1 Private Chat &amp; File Sharing</t>
+        </is>
+      </c>
+      <c r="D31" s="19" t="inlineStr">
+        <is>
+          <t>Open 💬 Chat from the bottom dock. → Switch the recipient from Everyone to a student's name to whisper 1:1. → Use the 📎 file button to upload a PDF, photo, or document — a download card appears for them. → Received files are saved with the card's ⬇ Save button.</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>Perfect for quietly asking a question without interrupting anyone else.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="54" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>🗓️</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Requesting a Postpone / Change</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>Pick the class in My Page → class schedule. → Press Request postpone/change and write the reason and preferred time. → After admin approval it's applied to the schedule automatically — you can track the status too.</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>Offering 2–3 preferred times gets you approved much faster.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="54" customHeight="1">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>🧾</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>Checking My Lesson-Fee Settlement</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>Open the 🧾 Settlement tab in My Page. → Check this month's class count and settlement amount. → Switch the month to review previous months as well.</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>Make it a habit to skim last month's statement at the start of each month.</t>
         </is>
       </c>
     </row>
@@ -1965,7 +2073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F302"/>
+  <dimension ref="A1:F347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5301,284 +5409,823 @@
       <c r="E302" s="33" t="n"/>
       <c r="F302" s="33" t="n"/>
     </row>
+    <row r="304" ht="26" customHeight="1">
+      <c r="A304" s="21" t="inlineStr">
+        <is>
+          <t>27  🔄 Tab Sync (Your Screen Leads)  —  Switch a tab and students follow instantly</t>
+        </is>
+      </c>
+      <c r="B304" s="22" t="n"/>
+      <c r="C304" s="22" t="n"/>
+      <c r="D304" s="22" t="n"/>
+      <c r="E304" s="22" t="n"/>
+      <c r="F304" s="22" t="n"/>
+    </row>
+    <row r="305" ht="42" customHeight="1">
+      <c r="A305" s="23" t="inlineStr">
+        <is>
+          <t>📖 When you switch top tabs — Board → Video → Review Quiz — the students' screens follow to the same tab automatically. No more saying “tap the ○○ tab”; you carry the lesson flow yourself.</t>
+        </is>
+      </c>
+      <c r="B305" s="24" t="n"/>
+      <c r="C305" s="24" t="n"/>
+      <c r="D305" s="24" t="n"/>
+      <c r="E305" s="24" t="n"/>
+      <c r="F305" s="24" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B306" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="30" customHeight="1">
+      <c r="A307" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B307" s="28" t="inlineStr">
+        <is>
+          <t>Switch the top tabs as usual (Board · Video · Games · Background · AI Warm-up · Review Quiz).</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="30" customHeight="1">
+      <c r="A308" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B308" s="28" t="inlineStr">
+        <is>
+          <t>Watch the student's screen switch to the same tab automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="30" customHeight="1">
+      <c r="A309" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B309" s="28" t="inlineStr">
+        <is>
+          <t>Textbook and file sharing carry over to students the same way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="24" customHeight="1">
+      <c r="A310" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B310" s="30" t="inlineStr">
+        <is>
+          <t>Even young learners follow along without hunting for buttons.</t>
+        </is>
+      </c>
+      <c r="C310" s="31" t="n"/>
+      <c r="D310" s="31" t="n"/>
+      <c r="E310" s="31" t="n"/>
+      <c r="F310" s="31" t="n"/>
+    </row>
+    <row r="311" ht="24" customHeight="1">
+      <c r="A311" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B311" s="30" t="inlineStr">
+        <is>
+          <t>The lesson rhythm never breaks, so pacing gets faster.</t>
+        </is>
+      </c>
+      <c r="C311" s="31" t="n"/>
+      <c r="D311" s="31" t="n"/>
+      <c r="E311" s="31" t="n"/>
+      <c r="F311" s="31" t="n"/>
+    </row>
+    <row r="312" ht="26" customHeight="1">
+      <c r="A312" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · Sync works while you're in the room together. If a screen doesn't follow, ask the student to re-enter.</t>
+        </is>
+      </c>
+      <c r="B312" s="35" t="n"/>
+      <c r="C312" s="35" t="n"/>
+      <c r="D312" s="35" t="n"/>
+      <c r="E312" s="35" t="n"/>
+      <c r="F312" s="35" t="n"/>
+    </row>
+    <row r="313" ht="30" customHeight="1">
+      <c r="A313" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · A quick heads-up before jumping to a video or quiz keeps students from being startled.</t>
+        </is>
+      </c>
+      <c r="B313" s="33" t="n"/>
+      <c r="C313" s="33" t="n"/>
+      <c r="D313" s="33" t="n"/>
+      <c r="E313" s="33" t="n"/>
+      <c r="F313" s="33" t="n"/>
+    </row>
+    <row r="315" ht="26" customHeight="1">
+      <c r="A315" s="21" t="inlineStr">
+        <is>
+          <t>28  💬 1:1 Private Chat &amp; File Sharing  —  Whisper messages only your student sees + share any file</t>
+        </is>
+      </c>
+      <c r="B315" s="22" t="n"/>
+      <c r="C315" s="22" t="n"/>
+      <c r="D315" s="22" t="n"/>
+      <c r="E315" s="22" t="n"/>
+      <c r="F315" s="22" t="n"/>
+    </row>
+    <row r="316" ht="42" customHeight="1">
+      <c r="A316" s="23" t="inlineStr">
+        <is>
+          <t>📖 Class chat now supports 1:1 private messages (DM). Send a message only a specific student can see, and share any file — PDF, image, document — through chat; it appears on the other side as a download card.</t>
+        </is>
+      </c>
+      <c r="B316" s="24" t="n"/>
+      <c r="C316" s="24" t="n"/>
+      <c r="D316" s="24" t="n"/>
+      <c r="E316" s="24" t="n"/>
+      <c r="F316" s="24" t="n"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B317" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="30" customHeight="1">
+      <c r="A318" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B318" s="28" t="inlineStr">
+        <is>
+          <t>Open 💬 Chat from the bottom dock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="30" customHeight="1">
+      <c r="A319" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B319" s="28" t="inlineStr">
+        <is>
+          <t>Switch the recipient from Everyone to a student's name to whisper 1:1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="30" customHeight="1">
+      <c r="A320" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B320" s="28" t="inlineStr">
+        <is>
+          <t>Use the 📎 file button to upload a PDF, photo, or document — a download card appears for them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="30" customHeight="1">
+      <c r="A321" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B321" s="28" t="inlineStr">
+        <is>
+          <t>Received files are saved with the card's ⬇ Save button.</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="24" customHeight="1">
+      <c r="A322" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B322" s="30" t="inlineStr">
+        <is>
+          <t>Private chats are visible only to the two of you.</t>
+        </is>
+      </c>
+      <c r="C322" s="31" t="n"/>
+      <c r="D322" s="31" t="n"/>
+      <c r="E322" s="31" t="n"/>
+      <c r="F322" s="31" t="n"/>
+    </row>
+    <row r="323" ht="24" customHeight="1">
+      <c r="A323" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B323" s="30" t="inlineStr">
+        <is>
+          <t>Homework files and notes get exchanged in one step during class.</t>
+        </is>
+      </c>
+      <c r="C323" s="31" t="n"/>
+      <c r="D323" s="31" t="n"/>
+      <c r="E323" s="31" t="n"/>
+      <c r="F323" s="31" t="n"/>
+    </row>
+    <row r="324" ht="26" customHeight="1">
+      <c r="A324" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · Private chats are not stored on the server and disappear after class. Keep important things as files.</t>
+        </is>
+      </c>
+      <c r="B324" s="35" t="n"/>
+      <c r="C324" s="35" t="n"/>
+      <c r="D324" s="35" t="n"/>
+      <c r="E324" s="35" t="n"/>
+      <c r="F324" s="35" t="n"/>
+    </row>
+    <row r="325" ht="30" customHeight="1">
+      <c r="A325" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Perfect for quietly asking a question without interrupting anyone else.</t>
+        </is>
+      </c>
+      <c r="B325" s="33" t="n"/>
+      <c r="C325" s="33" t="n"/>
+      <c r="D325" s="33" t="n"/>
+      <c r="E325" s="33" t="n"/>
+      <c r="F325" s="33" t="n"/>
+    </row>
+    <row r="327" ht="26" customHeight="1">
+      <c r="A327" s="21" t="inlineStr">
+        <is>
+          <t>29  🗓️ Requesting a Postpone / Change  —  Something came up? Submit right on the site</t>
+        </is>
+      </c>
+      <c r="B327" s="22" t="n"/>
+      <c r="C327" s="22" t="n"/>
+      <c r="D327" s="22" t="n"/>
+      <c r="E327" s="22" t="n"/>
+      <c r="F327" s="22" t="n"/>
+    </row>
+    <row r="328" ht="42" customHeight="1">
+      <c r="A328" s="23" t="inlineStr">
+        <is>
+          <t>📖 When something urgent comes up, you can now request a class postponement or time change right on the site. Your request reaches the admin in real time, and once approved it's applied to the schedule automatically.</t>
+        </is>
+      </c>
+      <c r="B328" s="24" t="n"/>
+      <c r="C328" s="24" t="n"/>
+      <c r="D328" s="24" t="n"/>
+      <c r="E328" s="24" t="n"/>
+      <c r="F328" s="24" t="n"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B329" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="30" customHeight="1">
+      <c r="A330" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B330" s="28" t="inlineStr">
+        <is>
+          <t>Pick the class in My Page → class schedule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="30" customHeight="1">
+      <c r="A331" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B331" s="28" t="inlineStr">
+        <is>
+          <t>Press Request postpone/change and write the reason and preferred time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="30" customHeight="1">
+      <c r="A332" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B332" s="28" t="inlineStr">
+        <is>
+          <t>After admin approval it's applied to the schedule automatically — you can track the status too.</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="24" customHeight="1">
+      <c r="A333" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B333" s="30" t="inlineStr">
+        <is>
+          <t>It's an official, recorded request — no phone calls or messengers needed.</t>
+        </is>
+      </c>
+      <c r="C333" s="31" t="n"/>
+      <c r="D333" s="31" t="n"/>
+      <c r="E333" s="31" t="n"/>
+      <c r="F333" s="31" t="n"/>
+    </row>
+    <row r="334" ht="24" customHeight="1">
+      <c r="A334" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B334" s="30" t="inlineStr">
+        <is>
+          <t>The original schedule holds until approval, so request early (ideally a day ahead).</t>
+        </is>
+      </c>
+      <c r="C334" s="31" t="n"/>
+      <c r="D334" s="31" t="n"/>
+      <c r="E334" s="31" t="n"/>
+      <c r="F334" s="31" t="n"/>
+    </row>
+    <row r="335" ht="26" customHeight="1">
+      <c r="A335" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · Last-minute changes need time to notify students and parents. If it's urgent, also alert support.</t>
+        </is>
+      </c>
+      <c r="B335" s="35" t="n"/>
+      <c r="C335" s="35" t="n"/>
+      <c r="D335" s="35" t="n"/>
+      <c r="E335" s="35" t="n"/>
+      <c r="F335" s="35" t="n"/>
+    </row>
+    <row r="336" ht="30" customHeight="1">
+      <c r="A336" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Offering 2–3 preferred times gets you approved much faster.</t>
+        </is>
+      </c>
+      <c r="B336" s="33" t="n"/>
+      <c r="C336" s="33" t="n"/>
+      <c r="D336" s="33" t="n"/>
+      <c r="E336" s="33" t="n"/>
+      <c r="F336" s="33" t="n"/>
+    </row>
+    <row r="338" ht="26" customHeight="1">
+      <c r="A338" s="21" t="inlineStr">
+        <is>
+          <t>30  🧾 Checking My Lesson-Fee Settlement  —  See this month's classes and pay yourself</t>
+        </is>
+      </c>
+      <c r="B338" s="22" t="n"/>
+      <c r="C338" s="22" t="n"/>
+      <c r="D338" s="22" t="n"/>
+      <c r="E338" s="22" t="n"/>
+      <c r="F338" s="22" t="n"/>
+    </row>
+    <row r="339" ht="42" customHeight="1">
+      <c r="A339" s="23" t="inlineStr">
+        <is>
+          <t>📖 In My Page's 🧾 Settlement tab, you can check this month's class count and lesson-fee settlement yourself. Settlement data is protected so only you can see yours, and past months are available too.</t>
+        </is>
+      </c>
+      <c r="B339" s="24" t="n"/>
+      <c r="C339" s="24" t="n"/>
+      <c r="D339" s="24" t="n"/>
+      <c r="E339" s="24" t="n"/>
+      <c r="F339" s="24" t="n"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B340" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="30" customHeight="1">
+      <c r="A341" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B341" s="28" t="inlineStr">
+        <is>
+          <t>Open the 🧾 Settlement tab in My Page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="30" customHeight="1">
+      <c r="A342" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B342" s="28" t="inlineStr">
+        <is>
+          <t>Check this month's class count and settlement amount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="30" customHeight="1">
+      <c r="A343" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B343" s="28" t="inlineStr">
+        <is>
+          <t>Switch the month to review previous months as well.</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="24" customHeight="1">
+      <c r="A344" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B344" s="30" t="inlineStr">
+        <is>
+          <t>Settlement details are visible only to you — safe and private.</t>
+        </is>
+      </c>
+      <c r="C344" s="31" t="n"/>
+      <c r="D344" s="31" t="n"/>
+      <c r="E344" s="31" t="n"/>
+      <c r="F344" s="31" t="n"/>
+    </row>
+    <row r="345" ht="24" customHeight="1">
+      <c r="A345" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B345" s="30" t="inlineStr">
+        <is>
+          <t>Class records connect to settlement automatically, so nothing gets missed.</t>
+        </is>
+      </c>
+      <c r="C345" s="31" t="n"/>
+      <c r="D345" s="31" t="n"/>
+      <c r="E345" s="31" t="n"/>
+      <c r="F345" s="31" t="n"/>
+    </row>
+    <row r="346" ht="26" customHeight="1">
+      <c r="A346" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · If a figure looks wrong, don't fix it yourself — contact the admin (HQ).</t>
+        </is>
+      </c>
+      <c r="B346" s="35" t="n"/>
+      <c r="C346" s="35" t="n"/>
+      <c r="D346" s="35" t="n"/>
+      <c r="E346" s="35" t="n"/>
+      <c r="F346" s="35" t="n"/>
+    </row>
+    <row r="347" ht="30" customHeight="1">
+      <c r="A347" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Make it a habit to skim last month's statement at the start of each month.</t>
+        </is>
+      </c>
+      <c r="B347" s="33" t="n"/>
+      <c r="C347" s="33" t="n"/>
+      <c r="D347" s="33" t="n"/>
+      <c r="E347" s="33" t="n"/>
+      <c r="F347" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="276">
+  <mergeCells count="317">
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B122:F122"/>
+    <mergeCell ref="B276:F276"/>
+    <mergeCell ref="B214:F214"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B253:F253"/>
+    <mergeCell ref="B342:F342"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A280:F280"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A249:F249"/>
+    <mergeCell ref="A347:F347"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A338:F338"/>
+    <mergeCell ref="A257:F257"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="A107:F107"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B133:F133"/>
+    <mergeCell ref="A315:F315"/>
+    <mergeCell ref="B160:F160"/>
+    <mergeCell ref="B135:F135"/>
+    <mergeCell ref="B306:F306"/>
+    <mergeCell ref="B233:F233"/>
+    <mergeCell ref="B224:F224"/>
+    <mergeCell ref="B72:F72"/>
+    <mergeCell ref="A267:F267"/>
+    <mergeCell ref="B70:F70"/>
+    <mergeCell ref="A269:F269"/>
+    <mergeCell ref="B293:F293"/>
+    <mergeCell ref="B322:F322"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B88:F88"/>
+    <mergeCell ref="B82:F82"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A199:F199"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B317:F317"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B254:F254"/>
+    <mergeCell ref="B319:F319"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="A346:F346"/>
+    <mergeCell ref="A90:F90"/>
+    <mergeCell ref="A217:F217"/>
+    <mergeCell ref="B141:F141"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="A129:F129"/>
+    <mergeCell ref="B272:F272"/>
+    <mergeCell ref="B136:F136"/>
+    <mergeCell ref="B299:F299"/>
+    <mergeCell ref="B225:F225"/>
+    <mergeCell ref="B274:F274"/>
+    <mergeCell ref="B243:F243"/>
+    <mergeCell ref="A270:F270"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A207:F207"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B154:F154"/>
+    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="A65:F65"/>
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B155:F155"/>
+    <mergeCell ref="B264:F264"/>
+    <mergeCell ref="B320:F320"/>
+    <mergeCell ref="A302:F302"/>
+    <mergeCell ref="B86:F86"/>
+    <mergeCell ref="B262:F262"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A327:F327"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="A220:F220"/>
+    <mergeCell ref="B246:F246"/>
+    <mergeCell ref="B211:F211"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="A197:F197"/>
+    <mergeCell ref="B275:F275"/>
+    <mergeCell ref="B340:F340"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B252:F252"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A150:F150"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B234:F234"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B172:F172"/>
+    <mergeCell ref="A289:F289"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B288:F288"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="A291:F291"/>
+    <mergeCell ref="B265:F265"/>
+    <mergeCell ref="A305:F305"/>
+    <mergeCell ref="A292:F292"/>
+    <mergeCell ref="B54:F54"/>
+    <mergeCell ref="B125:F125"/>
+    <mergeCell ref="B185:F185"/>
+    <mergeCell ref="B56:F56"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B341:F341"/>
+    <mergeCell ref="B120:F120"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B171:F171"/>
+    <mergeCell ref="A176:F176"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B204:F204"/>
+    <mergeCell ref="B296:F296"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B271:F271"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B62:F62"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B202:F202"/>
+    <mergeCell ref="B273:F273"/>
+    <mergeCell ref="A313:F313"/>
+    <mergeCell ref="A165:F165"/>
+    <mergeCell ref="A336:F336"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="A229:F229"/>
+    <mergeCell ref="B255:F255"/>
+    <mergeCell ref="B226:F226"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B284:F284"/>
+    <mergeCell ref="B222:F222"/>
+    <mergeCell ref="B344:F344"/>
+    <mergeCell ref="A339:F339"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B221:F221"/>
+    <mergeCell ref="B110:F110"/>
+    <mergeCell ref="B286:F286"/>
+    <mergeCell ref="A128:F128"/>
+    <mergeCell ref="A219:F219"/>
+    <mergeCell ref="B297:F297"/>
+    <mergeCell ref="B235:F235"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="B103:F103"/>
+    <mergeCell ref="B205:F205"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="B169:F169"/>
+    <mergeCell ref="A187:F187"/>
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="A66:F66"/>
-    <mergeCell ref="B81:F81"/>
     <mergeCell ref="B194:F194"/>
     <mergeCell ref="A118:F118"/>
-    <mergeCell ref="B252:F252"/>
     <mergeCell ref="A189:F189"/>
-    <mergeCell ref="B261:F261"/>
-    <mergeCell ref="B122:F122"/>
-    <mergeCell ref="A50:F50"/>
     <mergeCell ref="B71:F71"/>
-    <mergeCell ref="B184:F184"/>
-    <mergeCell ref="A3:F3"/>
     <mergeCell ref="B131:F131"/>
     <mergeCell ref="B236:F236"/>
-    <mergeCell ref="B214:F214"/>
-    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B307:F307"/>
     <mergeCell ref="B58:F58"/>
-    <mergeCell ref="A239:F239"/>
     <mergeCell ref="B223:F223"/>
-    <mergeCell ref="B276:F276"/>
     <mergeCell ref="B294:F294"/>
-    <mergeCell ref="A301:F301"/>
     <mergeCell ref="B195:F195"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="A150:F150"/>
-    <mergeCell ref="B253:F253"/>
     <mergeCell ref="B60:F60"/>
     <mergeCell ref="B231:F231"/>
     <mergeCell ref="B287:F287"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B157:F157"/>
     <mergeCell ref="A200:F200"/>
-    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="B84:F84"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="B241:F241"/>
+    <mergeCell ref="A260:F260"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B142:F142"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B213:F213"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B242:F242"/>
+    <mergeCell ref="A335:F335"/>
+    <mergeCell ref="A151:F151"/>
+    <mergeCell ref="A126:F126"/>
+    <mergeCell ref="A259:F259"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="A240:F240"/>
+    <mergeCell ref="B318:F318"/>
+    <mergeCell ref="A190:F190"/>
+    <mergeCell ref="B333:F333"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B308:F308"/>
+    <mergeCell ref="B99:F99"/>
+    <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B310:F310"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="A137:F137"/>
+    <mergeCell ref="B232:F232"/>
+    <mergeCell ref="B321:F321"/>
+    <mergeCell ref="B215:F215"/>
+    <mergeCell ref="A139:F139"/>
+    <mergeCell ref="A210:F210"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="B263:F263"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B323:F323"/>
+    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="B244:F244"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B145:F145"/>
+    <mergeCell ref="A140:F140"/>
+    <mergeCell ref="B181:F181"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="B87:F87"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B245:F245"/>
+    <mergeCell ref="A279:F279"/>
+    <mergeCell ref="A94:F94"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B334:F334"/>
+    <mergeCell ref="B309:F309"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="A316:F316"/>
+    <mergeCell ref="B100:F100"/>
+    <mergeCell ref="B311:F311"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B102:F102"/>
+    <mergeCell ref="A209:F209"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B329:F329"/>
+    <mergeCell ref="A148:F148"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B266:F266"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B331:F331"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B330:F330"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="B261:F261"/>
+    <mergeCell ref="B184:F184"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A301:F301"/>
+    <mergeCell ref="A239:F239"/>
+    <mergeCell ref="B42:F42"/>
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="B166:F166"/>
-    <mergeCell ref="A280:F280"/>
     <mergeCell ref="A161:F161"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B172:F172"/>
-    <mergeCell ref="B234:F234"/>
-    <mergeCell ref="A249:F249"/>
-    <mergeCell ref="A289:F289"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B174:F174"/>
     <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="A40:F40"/>
     <mergeCell ref="B168:F168"/>
-    <mergeCell ref="B288:F288"/>
-    <mergeCell ref="B84:F84"/>
     <mergeCell ref="B143:F143"/>
-    <mergeCell ref="A257:F257"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="A107:F107"/>
-    <mergeCell ref="B241:F241"/>
-    <mergeCell ref="A260:F260"/>
-    <mergeCell ref="B6:F6"/>
     <mergeCell ref="B281:F281"/>
-    <mergeCell ref="A291:F291"/>
     <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B133:F133"/>
-    <mergeCell ref="B142:F142"/>
     <mergeCell ref="B256:F256"/>
-    <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B213:F213"/>
     <mergeCell ref="A250:F250"/>
-    <mergeCell ref="B265:F265"/>
-    <mergeCell ref="B160:F160"/>
     <mergeCell ref="A237:F237"/>
-    <mergeCell ref="B135:F135"/>
     <mergeCell ref="A41:F41"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B233:F233"/>
-    <mergeCell ref="B242:F242"/>
     <mergeCell ref="A277:F277"/>
-    <mergeCell ref="B224:F224"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="A292:F292"/>
-    <mergeCell ref="B125:F125"/>
-    <mergeCell ref="B72:F72"/>
-    <mergeCell ref="B185:F185"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A267:F267"/>
     <mergeCell ref="B121:F121"/>
-    <mergeCell ref="B56:F56"/>
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B167:F167"/>
-    <mergeCell ref="B70:F70"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="A269:F269"/>
-    <mergeCell ref="A151:F151"/>
+    <mergeCell ref="B332:F332"/>
     <mergeCell ref="B111:F111"/>
-    <mergeCell ref="B293:F293"/>
-    <mergeCell ref="B120:F120"/>
-    <mergeCell ref="A126:F126"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="A259:F259"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="A240:F240"/>
-    <mergeCell ref="B17:F17"/>
     <mergeCell ref="B175:F175"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B88:F88"/>
-    <mergeCell ref="B82:F82"/>
-    <mergeCell ref="A190:F190"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="B171:F171"/>
-    <mergeCell ref="A199:F199"/>
     <mergeCell ref="A230:F230"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B99:F99"/>
-    <mergeCell ref="A176:F176"/>
-    <mergeCell ref="B295:F295"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B83:F83"/>
     <mergeCell ref="A11:F11"/>
-    <mergeCell ref="B254:F254"/>
-    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="A304:F304"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="A79:F79"/>
     <mergeCell ref="B251:F251"/>
-    <mergeCell ref="B204:F204"/>
     <mergeCell ref="B45:F45"/>
     <mergeCell ref="B216:F216"/>
-    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B343:F343"/>
     <mergeCell ref="A162:F162"/>
-    <mergeCell ref="B296:F296"/>
-    <mergeCell ref="B173:F173"/>
     <mergeCell ref="A227:F227"/>
-    <mergeCell ref="B271:F271"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="A137:F137"/>
     <mergeCell ref="B109:F109"/>
     <mergeCell ref="A177:F177"/>
     <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B62:F62"/>
-    <mergeCell ref="A90:F90"/>
-    <mergeCell ref="A217:F217"/>
-    <mergeCell ref="B232:F232"/>
-    <mergeCell ref="B141:F141"/>
+    <mergeCell ref="B345:F345"/>
     <mergeCell ref="A164:F164"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B193:F193"/>
-    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B295:F295"/>
     <mergeCell ref="B46:F46"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B202:F202"/>
-    <mergeCell ref="B215:F215"/>
-    <mergeCell ref="A139:F139"/>
-    <mergeCell ref="B273:F273"/>
-    <mergeCell ref="A210:F210"/>
     <mergeCell ref="B282:F282"/>
     <mergeCell ref="A179:F179"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="A129:F129"/>
-    <mergeCell ref="B263:F263"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B272:F272"/>
-    <mergeCell ref="A76:F76"/>
     <mergeCell ref="B48:F48"/>
     <mergeCell ref="A116:F116"/>
-    <mergeCell ref="B244:F244"/>
-    <mergeCell ref="B136:F136"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="B145:F145"/>
-    <mergeCell ref="A140:F140"/>
     <mergeCell ref="A53:F53"/>
-    <mergeCell ref="B181:F181"/>
-    <mergeCell ref="A165:F165"/>
+    <mergeCell ref="A324:F324"/>
     <mergeCell ref="A180:F180"/>
-    <mergeCell ref="B225:F225"/>
-    <mergeCell ref="B274:F274"/>
-    <mergeCell ref="B299:F299"/>
-    <mergeCell ref="A63:F63"/>
     <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B243:F243"/>
-    <mergeCell ref="B87:F87"/>
     <mergeCell ref="A93:F93"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B245:F245"/>
-    <mergeCell ref="A229:F229"/>
-    <mergeCell ref="B255:F255"/>
-    <mergeCell ref="B226:F226"/>
-    <mergeCell ref="A270:F270"/>
-    <mergeCell ref="A279:F279"/>
+    <mergeCell ref="A328:F328"/>
     <mergeCell ref="B300:F300"/>
     <mergeCell ref="B183:F183"/>
-    <mergeCell ref="A49:F49"/>
-    <mergeCell ref="B192:F192"/>
     <mergeCell ref="B201:F201"/>
-    <mergeCell ref="A207:F207"/>
-    <mergeCell ref="B284:F284"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A94:F94"/>
-    <mergeCell ref="B222:F222"/>
     <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B154:F154"/>
-    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="B212:F212"/>
     <mergeCell ref="B206:F206"/>
-    <mergeCell ref="B212:F212"/>
-    <mergeCell ref="B110:F110"/>
     <mergeCell ref="B203:F203"/>
-    <mergeCell ref="B221:F221"/>
-    <mergeCell ref="A65:F65"/>
-    <mergeCell ref="B286:F286"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="A128:F128"/>
-    <mergeCell ref="B100:F100"/>
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B155:F155"/>
-    <mergeCell ref="B264:F264"/>
-    <mergeCell ref="B102:F102"/>
     <mergeCell ref="A104:F104"/>
     <mergeCell ref="B130:F130"/>
-    <mergeCell ref="A302:F302"/>
     <mergeCell ref="A247:F247"/>
-    <mergeCell ref="B86:F86"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="B262:F262"/>
-    <mergeCell ref="A219:F219"/>
-    <mergeCell ref="B297:F297"/>
-    <mergeCell ref="B235:F235"/>
+    <mergeCell ref="A312:F312"/>
     <mergeCell ref="A106:F106"/>
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="B61:F61"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B132:F132"/>
-    <mergeCell ref="A209:F209"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="A52:F52"/>
     <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B103:F103"/>
     <mergeCell ref="B196:F196"/>
     <mergeCell ref="B112:F112"/>
-    <mergeCell ref="B205:F205"/>
     <mergeCell ref="B283:F283"/>
-    <mergeCell ref="A220:F220"/>
-    <mergeCell ref="B246:F246"/>
     <mergeCell ref="B298:F298"/>
-    <mergeCell ref="B211:F211"/>
-    <mergeCell ref="A148:F148"/>
     <mergeCell ref="B285:F285"/>
-    <mergeCell ref="B55:F55"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B266:F266"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="A197:F197"/>
-    <mergeCell ref="B169:F169"/>
-    <mergeCell ref="B275:F275"/>
+    <mergeCell ref="A325:F325"/>
     <mergeCell ref="A119:F119"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="A187:F187"/>
-    <mergeCell ref="B97:F97"/>
     <mergeCell ref="A25:F25"/>
-    <mergeCell ref="B35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloudflare-deploy/public/library/teacher/teacher-en.xlsx
+++ b/cloudflare-deploy/public/library/teacher/teacher-en.xlsx
@@ -1205,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2056,6 +2056,168 @@
       <c r="E33" s="20" t="inlineStr">
         <is>
           <t>Make it a habit to skim last month's statement at the start of each month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="54" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>🔒</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>Three class controls (focus · background lock · exit guard)</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>Open ⚙️ Settings in the bottom dock of the lesson screen. → Turn on Focus mode to pin the student's screen to the lesson. → Turn on Background lock so backgrounds and face decorations can't be changed. → Leave Exit guard on and the student is asked to confirm before leaving. → All three release automatically when the lesson ends.</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>Rather than switching them on only for restless students, leave them on from lesson one — it feels more natural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="54" customHeight="1">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>✍️</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>Textbook PDF — annotations that stay · faster page jumps</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>Open the Textbook tab and load the PDF. → Underline and circle with the writing tools. → Move with ◀ ▶, or type a page number to jump. → Go back a page and your earlier marks are still there. → If the screen feels slow, turn on light mode.</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>Note down the page numbers you use most before class and jumping becomes instant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="54" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>🔉</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>It rides out a slow connection by itself</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>There is nothing to press — it happens automatically. → If the picture blurs or freezes, carry on by voice. → Video returns on its own once the line improves. → If it stays unstable, ask the student to move closer to their Wi-Fi.</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>For students who drop often, have them run the device check screen once before class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="54" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>🧠</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>Using Judgment Training in class</t>
+        </is>
+      </c>
+      <c r="D37" s="19" t="inlineStr">
+        <is>
+          <t>Ask the student to open 🧠 Judgment Training and solve one question together. → Have them read out their choice and the reason they wrote. → Explain why the other options fit less well — by listener, tone, and situation. → After class, check the judgment index trend in the student report.</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr">
+        <is>
+          <t>Ask “Why did you think so?” in English and let them answer in their own language. The reasoning comes first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="54" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>🎥</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>Replay a recorded lesson</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>Press REC at the top during the lesson to record. → After class, find the lesson under Lesson log / Recordings. → Press ▶ Play to review it right there. → If a parent needs a copy, ask an administrator.</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>Watching five minutes of your own lesson afterwards visibly improves your pace and question ratio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="54" customHeight="1">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>🔑</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>Your account (password · interface language)</t>
+        </is>
+      </c>
+      <c r="D39" s="19" t="inlineStr">
+        <is>
+          <t>Forgot your password? Ask the admin (operations team) for a reset. → Once you receive a temporary password, log in and change it immediately. → Switch the interface language with the 🌐 EN / KR button at the top. → If you use the app, registering a face / fingerprint passkey is the easiest option.</t>
+        </is>
+      </c>
+      <c r="E39" s="20" t="inlineStr">
+        <is>
+          <t>If you forget passwords often, register an app passkey — a glance gets you in.</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F347"/>
+  <dimension ref="A1:F424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5907,8 +6069,880 @@
       <c r="E347" s="33" t="n"/>
       <c r="F347" s="33" t="n"/>
     </row>
+    <row r="349" ht="26" customHeight="1">
+      <c r="A349" s="21" t="inlineStr">
+        <is>
+          <t>31  🔒 Three class controls (focus · background lock · exit guard)  —  Fewer distractions and accidental exits</t>
+        </is>
+      </c>
+      <c r="B349" s="22" t="n"/>
+      <c r="C349" s="22" t="n"/>
+      <c r="D349" s="22" t="n"/>
+      <c r="E349" s="22" t="n"/>
+      <c r="F349" s="22" t="n"/>
+    </row>
+    <row r="350" ht="42" customHeight="1">
+      <c r="A350" s="23" t="inlineStr">
+        <is>
+          <t>📖 Three controls the teacher can switch on and off. Focus mode stops the student drifting to other screens during the lesson, background lock stops them changing backgrounds and face decorations over and over, and exit guard catches an accidental back-button press before they leave the lesson.</t>
+        </is>
+      </c>
+      <c r="B350" s="24" t="n"/>
+      <c r="C350" s="24" t="n"/>
+      <c r="D350" s="24" t="n"/>
+      <c r="E350" s="24" t="n"/>
+      <c r="F350" s="24" t="n"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B351" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="352" ht="30" customHeight="1">
+      <c r="A352" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B352" s="28" t="inlineStr">
+        <is>
+          <t>Open ⚙️ Settings in the bottom dock of the lesson screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="353" ht="30" customHeight="1">
+      <c r="A353" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B353" s="28" t="inlineStr">
+        <is>
+          <t>Turn on Focus mode to pin the student's screen to the lesson.</t>
+        </is>
+      </c>
+    </row>
+    <row r="354" ht="30" customHeight="1">
+      <c r="A354" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B354" s="28" t="inlineStr">
+        <is>
+          <t>Turn on Background lock so backgrounds and face decorations can't be changed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="355" ht="30" customHeight="1">
+      <c r="A355" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B355" s="28" t="inlineStr">
+        <is>
+          <t>Leave Exit guard on and the student is asked to confirm before leaving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="356" ht="30" customHeight="1">
+      <c r="A356" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B356" s="28" t="inlineStr">
+        <is>
+          <t>All three release automatically when the lesson ends.</t>
+        </is>
+      </c>
+    </row>
+    <row r="357" ht="24" customHeight="1">
+      <c r="A357" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B357" s="30" t="inlineStr">
+        <is>
+          <t>A brief disconnection does not end the lesson — the student picks up where they left off.</t>
+        </is>
+      </c>
+      <c r="C357" s="31" t="n"/>
+      <c r="D357" s="31" t="n"/>
+      <c r="E357" s="31" t="n"/>
+      <c r="F357" s="31" t="n"/>
+    </row>
+    <row r="358" ht="24" customHeight="1">
+      <c r="A358" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B358" s="30" t="inlineStr">
+        <is>
+          <t>No-shows are counted automatically and appear on the admin screen.</t>
+        </is>
+      </c>
+      <c r="C358" s="31" t="n"/>
+      <c r="D358" s="31" t="n"/>
+      <c r="E358" s="31" t="n"/>
+      <c r="F358" s="31" t="n"/>
+    </row>
+    <row r="359" ht="24" customHeight="1">
+      <c r="A359" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B359" s="30" t="inlineStr">
+        <is>
+          <t>Especially effective with younger classes.</t>
+        </is>
+      </c>
+      <c r="C359" s="31" t="n"/>
+      <c r="D359" s="31" t="n"/>
+      <c r="E359" s="31" t="n"/>
+      <c r="F359" s="31" t="n"/>
+    </row>
+    <row r="360" ht="26" customHeight="1">
+      <c r="A360" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · These are tools for helping focus, not for punishing. Explain them to the student at the start of the lesson.</t>
+        </is>
+      </c>
+      <c r="B360" s="35" t="n"/>
+      <c r="C360" s="35" t="n"/>
+      <c r="D360" s="35" t="n"/>
+      <c r="E360" s="35" t="n"/>
+      <c r="F360" s="35" t="n"/>
+    </row>
+    <row r="361" ht="30" customHeight="1">
+      <c r="A361" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Rather than switching them on only for restless students, leave them on from lesson one — it feels more natural.</t>
+        </is>
+      </c>
+      <c r="B361" s="33" t="n"/>
+      <c r="C361" s="33" t="n"/>
+      <c r="D361" s="33" t="n"/>
+      <c r="E361" s="33" t="n"/>
+      <c r="F361" s="33" t="n"/>
+    </row>
+    <row r="363" ht="26" customHeight="1">
+      <c r="A363" s="21" t="inlineStr">
+        <is>
+          <t>32  ✍️ Textbook PDF — annotations that stay · faster page jumps  —  Turn the page and come back; your marks are still there</t>
+        </is>
+      </c>
+      <c r="B363" s="22" t="n"/>
+      <c r="C363" s="22" t="n"/>
+      <c r="D363" s="22" t="n"/>
+      <c r="E363" s="22" t="n"/>
+      <c r="F363" s="22" t="n"/>
+    </row>
+    <row r="364" ht="42" customHeight="1">
+      <c r="A364" s="23" t="inlineStr">
+        <is>
+          <t>📖 Annotations you draw on a textbook PDF now survive turning the page and coming back. Navigation is faster with ◀ ▶ buttons and direct page-number entry, and a new light mode keeps page turns smooth on older devices and slow connections.</t>
+        </is>
+      </c>
+      <c r="B364" s="24" t="n"/>
+      <c r="C364" s="24" t="n"/>
+      <c r="D364" s="24" t="n"/>
+      <c r="E364" s="24" t="n"/>
+      <c r="F364" s="24" t="n"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B365" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="366" ht="30" customHeight="1">
+      <c r="A366" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B366" s="28" t="inlineStr">
+        <is>
+          <t>Open the Textbook tab and load the PDF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="367" ht="30" customHeight="1">
+      <c r="A367" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B367" s="28" t="inlineStr">
+        <is>
+          <t>Underline and circle with the writing tools.</t>
+        </is>
+      </c>
+    </row>
+    <row r="368" ht="30" customHeight="1">
+      <c r="A368" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B368" s="28" t="inlineStr">
+        <is>
+          <t>Move with ◀ ▶, or type a page number to jump.</t>
+        </is>
+      </c>
+    </row>
+    <row r="369" ht="30" customHeight="1">
+      <c r="A369" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B369" s="28" t="inlineStr">
+        <is>
+          <t>Go back a page and your earlier marks are still there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="370" ht="30" customHeight="1">
+      <c r="A370" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B370" s="28" t="inlineStr">
+        <is>
+          <t>If the screen feels slow, turn on light mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="371" ht="24" customHeight="1">
+      <c r="A371" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B371" s="30" t="inlineStr">
+        <is>
+          <t>Annotations are stored per page, so they never mix up.</t>
+        </is>
+      </c>
+      <c r="C371" s="31" t="n"/>
+      <c r="D371" s="31" t="n"/>
+      <c r="E371" s="31" t="n"/>
+      <c r="F371" s="31" t="n"/>
+    </row>
+    <row r="372" ht="24" customHeight="1">
+      <c r="A372" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B372" s="30" t="inlineStr">
+        <is>
+          <t>Light mode trades a little sharpness for much smoother page turns.</t>
+        </is>
+      </c>
+      <c r="C372" s="31" t="n"/>
+      <c r="D372" s="31" t="n"/>
+      <c r="E372" s="31" t="n"/>
+      <c r="F372" s="31" t="n"/>
+    </row>
+    <row r="373" ht="24" customHeight="1">
+      <c r="A373" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B373" s="30" t="inlineStr">
+        <is>
+          <t>The student sees the same page with the same annotations.</t>
+        </is>
+      </c>
+      <c r="C373" s="31" t="n"/>
+      <c r="D373" s="31" t="n"/>
+      <c r="E373" s="31" t="n"/>
+      <c r="F373" s="31" t="n"/>
+    </row>
+    <row r="374" ht="30" customHeight="1">
+      <c r="A374" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Note down the page numbers you use most before class and jumping becomes instant.</t>
+        </is>
+      </c>
+      <c r="B374" s="33" t="n"/>
+      <c r="C374" s="33" t="n"/>
+      <c r="D374" s="33" t="n"/>
+      <c r="E374" s="33" t="n"/>
+      <c r="F374" s="33" t="n"/>
+    </row>
+    <row r="376" ht="26" customHeight="1">
+      <c r="A376" s="21" t="inlineStr">
+        <is>
+          <t>33  🔉 It rides out a slow connection by itself  —  Video may fold away, but the voice keeps going</t>
+        </is>
+      </c>
+      <c r="B376" s="22" t="n"/>
+      <c r="C376" s="22" t="n"/>
+      <c r="D376" s="22" t="n"/>
+      <c r="E376" s="22" t="n"/>
+      <c r="F376" s="22" t="n"/>
+    </row>
+    <row r="377" ht="42" customHeight="1">
+      <c r="A377" s="23" t="inlineStr">
+        <is>
+          <t>📖 When the line degrades, the system lowers video quality by itself, and if that isn't enough it switches automatically to a voice-first (audio-only) mode so the lesson doesn't break. When the connection recovers, video comes back. Built with unstable connections — like on-site in the Philippines — in mind.</t>
+        </is>
+      </c>
+      <c r="B377" s="24" t="n"/>
+      <c r="C377" s="24" t="n"/>
+      <c r="D377" s="24" t="n"/>
+      <c r="E377" s="24" t="n"/>
+      <c r="F377" s="24" t="n"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B378" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="379" ht="30" customHeight="1">
+      <c r="A379" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B379" s="28" t="inlineStr">
+        <is>
+          <t>There is nothing to press — it happens automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="380" ht="30" customHeight="1">
+      <c r="A380" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B380" s="28" t="inlineStr">
+        <is>
+          <t>If the picture blurs or freezes, carry on by voice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="381" ht="30" customHeight="1">
+      <c r="A381" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B381" s="28" t="inlineStr">
+        <is>
+          <t>Video returns on its own once the line improves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="382" ht="30" customHeight="1">
+      <c r="A382" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B382" s="28" t="inlineStr">
+        <is>
+          <t>If it stays unstable, ask the student to move closer to their Wi-Fi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="383" ht="24" customHeight="1">
+      <c r="A383" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B383" s="30" t="inlineStr">
+        <is>
+          <t>Voice is protected to the very last — the lesson can continue by speech alone.</t>
+        </is>
+      </c>
+      <c r="C383" s="31" t="n"/>
+      <c r="D383" s="31" t="n"/>
+      <c r="E383" s="31" t="n"/>
+      <c r="F383" s="31" t="n"/>
+    </row>
+    <row r="384" ht="24" customHeight="1">
+      <c r="A384" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B384" s="30" t="inlineStr">
+        <is>
+          <t>A brief drop never auto-ends the lesson.</t>
+        </is>
+      </c>
+      <c r="C384" s="31" t="n"/>
+      <c r="D384" s="31" t="n"/>
+      <c r="E384" s="31" t="n"/>
+      <c r="F384" s="31" t="n"/>
+    </row>
+    <row r="385" ht="24" customHeight="1">
+      <c r="A385" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B385" s="30" t="inlineStr">
+        <is>
+          <t>If the far side freezes to black, it attempts self-recovery.</t>
+        </is>
+      </c>
+      <c r="C385" s="31" t="n"/>
+      <c r="D385" s="31" t="n"/>
+      <c r="E385" s="31" t="n"/>
+      <c r="F385" s="31" t="n"/>
+    </row>
+    <row r="386" ht="26" customHeight="1">
+      <c r="A386" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · If nothing returns after 90 seconds, a notice card appears. That's the moment to contact the student.</t>
+        </is>
+      </c>
+      <c r="B386" s="35" t="n"/>
+      <c r="C386" s="35" t="n"/>
+      <c r="D386" s="35" t="n"/>
+      <c r="E386" s="35" t="n"/>
+      <c r="F386" s="35" t="n"/>
+    </row>
+    <row r="387" ht="30" customHeight="1">
+      <c r="A387" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · For students who drop often, have them run the device check screen once before class.</t>
+        </is>
+      </c>
+      <c r="B387" s="33" t="n"/>
+      <c r="C387" s="33" t="n"/>
+      <c r="D387" s="33" t="n"/>
+      <c r="E387" s="33" t="n"/>
+      <c r="F387" s="33" t="n"/>
+    </row>
+    <row r="389" ht="26" customHeight="1">
+      <c r="A389" s="21" t="inlineStr">
+        <is>
+          <t>34  🧠 Using Judgment Training in class  —  Turn the student's reasoning into lesson material</t>
+        </is>
+      </c>
+      <c r="B389" s="22" t="n"/>
+      <c r="C389" s="22" t="n"/>
+      <c r="D389" s="22" t="n"/>
+      <c r="E389" s="22" t="n"/>
+      <c r="F389" s="22" t="n"/>
+    </row>
+    <row r="390" ht="42" customHeight="1">
+      <c r="A390" s="23" t="inlineStr">
+        <is>
+          <t>📖 Judgment Training works well as an in-class activity. Because the student's choice and their stated reason are both recorded, you can respond to *how they thought* rather than just right/wrong. Judgments made during class feed into the student's growth metrics.</t>
+        </is>
+      </c>
+      <c r="B390" s="24" t="n"/>
+      <c r="C390" s="24" t="n"/>
+      <c r="D390" s="24" t="n"/>
+      <c r="E390" s="24" t="n"/>
+      <c r="F390" s="24" t="n"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B391" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="392" ht="30" customHeight="1">
+      <c r="A392" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B392" s="28" t="inlineStr">
+        <is>
+          <t>Ask the student to open 🧠 Judgment Training and solve one question together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="393" ht="30" customHeight="1">
+      <c r="A393" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B393" s="28" t="inlineStr">
+        <is>
+          <t>Have them read out their choice and the reason they wrote.</t>
+        </is>
+      </c>
+    </row>
+    <row r="394" ht="30" customHeight="1">
+      <c r="A394" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B394" s="28" t="inlineStr">
+        <is>
+          <t>Explain why the other options fit less well — by listener, tone, and situation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="395" ht="30" customHeight="1">
+      <c r="A395" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B395" s="28" t="inlineStr">
+        <is>
+          <t>After class, check the judgment index trend in the student report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="396" ht="24" customHeight="1">
+      <c r="A396" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B396" s="30" t="inlineStr">
+        <is>
+          <t>Partial credit means a near-miss still earns points — students don't feel punished.</t>
+        </is>
+      </c>
+      <c r="C396" s="31" t="n"/>
+      <c r="D396" s="31" t="n"/>
+      <c r="E396" s="31" t="n"/>
+      <c r="F396" s="31" t="n"/>
+    </row>
+    <row r="397" ht="24" customHeight="1">
+      <c r="A397" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B397" s="30" t="inlineStr">
+        <is>
+          <t>Recent answers are weighted more heavily, so a student who improves lately climbs quickly.</t>
+        </is>
+      </c>
+      <c r="C397" s="31" t="n"/>
+      <c r="D397" s="31" t="n"/>
+      <c r="E397" s="31" t="n"/>
+      <c r="F397" s="31" t="n"/>
+    </row>
+    <row r="398" ht="24" customHeight="1">
+      <c r="A398" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B398" s="30" t="inlineStr">
+        <is>
+          <t>Students who recover after a wrong answer are identified separately.</t>
+        </is>
+      </c>
+      <c r="C398" s="31" t="n"/>
+      <c r="D398" s="31" t="n"/>
+      <c r="E398" s="31" t="n"/>
+      <c r="F398" s="31" t="n"/>
+    </row>
+    <row r="399" ht="30" customHeight="1">
+      <c r="A399" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Ask “Why did you think so?” in English and let them answer in their own language. The reasoning comes first.</t>
+        </is>
+      </c>
+      <c r="B399" s="33" t="n"/>
+      <c r="C399" s="33" t="n"/>
+      <c r="D399" s="33" t="n"/>
+      <c r="E399" s="33" t="n"/>
+      <c r="F399" s="33" t="n"/>
+    </row>
+    <row r="401" ht="26" customHeight="1">
+      <c r="A401" s="21" t="inlineStr">
+        <is>
+          <t>35  🎥 Replay a recorded lesson  —  Play back a recording where you found it</t>
+        </is>
+      </c>
+      <c r="B401" s="22" t="n"/>
+      <c r="C401" s="22" t="n"/>
+      <c r="D401" s="22" t="n"/>
+      <c r="E401" s="22" t="n"/>
+      <c r="F401" s="22" t="n"/>
+    </row>
+    <row r="402" ht="42" customHeight="1">
+      <c r="A402" s="23" t="inlineStr">
+        <is>
+          <t>📖 A lesson recorded with REC can now be played back directly from the management screen. No download needed — one click plays it, and the old bug that threw you back to the login screen is fixed.</t>
+        </is>
+      </c>
+      <c r="B402" s="24" t="n"/>
+      <c r="C402" s="24" t="n"/>
+      <c r="D402" s="24" t="n"/>
+      <c r="E402" s="24" t="n"/>
+      <c r="F402" s="24" t="n"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B403" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="404" ht="30" customHeight="1">
+      <c r="A404" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B404" s="28" t="inlineStr">
+        <is>
+          <t>Press REC at the top during the lesson to record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="405" ht="30" customHeight="1">
+      <c r="A405" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B405" s="28" t="inlineStr">
+        <is>
+          <t>After class, find the lesson under Lesson log / Recordings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="406" ht="30" customHeight="1">
+      <c r="A406" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B406" s="28" t="inlineStr">
+        <is>
+          <t>Press ▶ Play to review it right there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="407" ht="30" customHeight="1">
+      <c r="A407" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B407" s="28" t="inlineStr">
+        <is>
+          <t>If a parent needs a copy, ask an administrator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="408" ht="24" customHeight="1">
+      <c r="A408" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B408" s="30" t="inlineStr">
+        <is>
+          <t>Playback no longer bounces you to the login screen.</t>
+        </is>
+      </c>
+      <c r="C408" s="31" t="n"/>
+      <c r="D408" s="31" t="n"/>
+      <c r="E408" s="31" t="n"/>
+      <c r="F408" s="31" t="n"/>
+    </row>
+    <row r="409" ht="24" customHeight="1">
+      <c r="A409" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B409" s="30" t="inlineStr">
+        <is>
+          <t>Recordings are kept on the server and cleaned up per the storage policy.</t>
+        </is>
+      </c>
+      <c r="C409" s="31" t="n"/>
+      <c r="D409" s="31" t="n"/>
+      <c r="E409" s="31" t="n"/>
+      <c r="F409" s="31" t="n"/>
+    </row>
+    <row r="410" ht="24" customHeight="1">
+      <c r="A410" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B410" s="30" t="inlineStr">
+        <is>
+          <t>They contain student faces — external sharing is prohibited.</t>
+        </is>
+      </c>
+      <c r="C410" s="31" t="n"/>
+      <c r="D410" s="31" t="n"/>
+      <c r="E410" s="31" t="n"/>
+      <c r="F410" s="31" t="n"/>
+    </row>
+    <row r="411" ht="26" customHeight="1">
+      <c r="A411" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · Record only with student and parent consent.</t>
+        </is>
+      </c>
+      <c r="B411" s="35" t="n"/>
+      <c r="C411" s="35" t="n"/>
+      <c r="D411" s="35" t="n"/>
+      <c r="E411" s="35" t="n"/>
+      <c r="F411" s="35" t="n"/>
+    </row>
+    <row r="412" ht="30" customHeight="1">
+      <c r="A412" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Watching five minutes of your own lesson afterwards visibly improves your pace and question ratio.</t>
+        </is>
+      </c>
+      <c r="B412" s="33" t="n"/>
+      <c r="C412" s="33" t="n"/>
+      <c r="D412" s="33" t="n"/>
+      <c r="E412" s="33" t="n"/>
+      <c r="F412" s="33" t="n"/>
+    </row>
+    <row r="414" ht="26" customHeight="1">
+      <c r="A414" s="21" t="inlineStr">
+        <is>
+          <t>36  🔑 Your account (password · interface language)  —  When you forget your password · English screen</t>
+        </is>
+      </c>
+      <c r="B414" s="22" t="n"/>
+      <c r="C414" s="22" t="n"/>
+      <c r="D414" s="22" t="n"/>
+      <c r="E414" s="22" t="n"/>
+      <c r="F414" s="22" t="n"/>
+    </row>
+    <row r="415" ht="42" customHeight="1">
+      <c r="A415" s="23" t="inlineStr">
+        <is>
+          <t>📖 If you forget your password, ask an administrator and it's reset straight away. Teacher accounts also now always open in English, so no one gets lost looking for a menu on a Korean screen.</t>
+        </is>
+      </c>
+      <c r="B415" s="24" t="n"/>
+      <c r="C415" s="24" t="n"/>
+      <c r="D415" s="24" t="n"/>
+      <c r="E415" s="24" t="n"/>
+      <c r="F415" s="24" t="n"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B416" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="417" ht="30" customHeight="1">
+      <c r="A417" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B417" s="28" t="inlineStr">
+        <is>
+          <t>Forgot your password? Ask the admin (operations team) for a reset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="418" ht="30" customHeight="1">
+      <c r="A418" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B418" s="28" t="inlineStr">
+        <is>
+          <t>Once you receive a temporary password, log in and change it immediately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="419" ht="30" customHeight="1">
+      <c r="A419" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B419" s="28" t="inlineStr">
+        <is>
+          <t>Switch the interface language with the 🌐 EN / KR button at the top.</t>
+        </is>
+      </c>
+    </row>
+    <row r="420" ht="30" customHeight="1">
+      <c r="A420" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B420" s="28" t="inlineStr">
+        <is>
+          <t>If you use the app, registering a face / fingerprint passkey is the easiest option.</t>
+        </is>
+      </c>
+    </row>
+    <row r="421" ht="24" customHeight="1">
+      <c r="A421" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B421" s="30" t="inlineStr">
+        <is>
+          <t>Teacher accounts default to the English interface.</t>
+        </is>
+      </c>
+      <c r="C421" s="31" t="n"/>
+      <c r="D421" s="31" t="n"/>
+      <c r="E421" s="31" t="n"/>
+      <c r="F421" s="31" t="n"/>
+    </row>
+    <row r="422" ht="24" customHeight="1">
+      <c r="A422" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B422" s="30" t="inlineStr">
+        <is>
+          <t>A language you pick yourself is saved to your account only.</t>
+        </is>
+      </c>
+      <c r="C422" s="31" t="n"/>
+      <c r="D422" s="31" t="n"/>
+      <c r="E422" s="31" t="n"/>
+      <c r="F422" s="31" t="n"/>
+    </row>
+    <row r="423" ht="24" customHeight="1">
+      <c r="A423" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B423" s="30" t="inlineStr">
+        <is>
+          <t>Always replace the temporary password.</t>
+        </is>
+      </c>
+      <c r="C423" s="31" t="n"/>
+      <c r="D423" s="31" t="n"/>
+      <c r="E423" s="31" t="n"/>
+      <c r="F423" s="31" t="n"/>
+    </row>
+    <row r="424" ht="30" customHeight="1">
+      <c r="A424" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · If you forget passwords often, register an app passkey — a glance gets you in.</t>
+        </is>
+      </c>
+      <c r="B424" s="33" t="n"/>
+      <c r="C424" s="33" t="n"/>
+      <c r="D424" s="33" t="n"/>
+      <c r="E424" s="33" t="n"/>
+      <c r="F424" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="317">
+  <mergeCells count="388">
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B122:F122"/>
     <mergeCell ref="B276:F276"/>
@@ -5926,20 +6960,28 @@
     <mergeCell ref="A257:F257"/>
     <mergeCell ref="B158:F158"/>
     <mergeCell ref="A107:F107"/>
+    <mergeCell ref="A349:F349"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B133:F133"/>
+    <mergeCell ref="B369:F369"/>
+    <mergeCell ref="B418:F418"/>
     <mergeCell ref="A315:F315"/>
+    <mergeCell ref="B356:F356"/>
     <mergeCell ref="B160:F160"/>
+    <mergeCell ref="B368:F368"/>
     <mergeCell ref="B135:F135"/>
     <mergeCell ref="B306:F306"/>
     <mergeCell ref="B233:F233"/>
+    <mergeCell ref="B420:F420"/>
     <mergeCell ref="B224:F224"/>
     <mergeCell ref="B72:F72"/>
+    <mergeCell ref="B370:F370"/>
     <mergeCell ref="A267:F267"/>
     <mergeCell ref="B70:F70"/>
     <mergeCell ref="A269:F269"/>
     <mergeCell ref="B293:F293"/>
     <mergeCell ref="B322:F322"/>
+    <mergeCell ref="A377:F377"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B88:F88"/>
     <mergeCell ref="B82:F82"/>
@@ -5952,11 +6994,14 @@
     <mergeCell ref="B254:F254"/>
     <mergeCell ref="B319:F319"/>
     <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B383:F383"/>
     <mergeCell ref="A346:F346"/>
     <mergeCell ref="A90:F90"/>
     <mergeCell ref="A217:F217"/>
     <mergeCell ref="B141:F141"/>
     <mergeCell ref="B159:F159"/>
+    <mergeCell ref="A415:F415"/>
+    <mergeCell ref="A390:F390"/>
     <mergeCell ref="A129:F129"/>
     <mergeCell ref="B272:F272"/>
     <mergeCell ref="B136:F136"/>
@@ -5964,6 +7009,7 @@
     <mergeCell ref="B225:F225"/>
     <mergeCell ref="B274:F274"/>
     <mergeCell ref="B243:F243"/>
+    <mergeCell ref="B373:F373"/>
     <mergeCell ref="A270:F270"/>
     <mergeCell ref="A49:F49"/>
     <mergeCell ref="A207:F207"/>
@@ -5971,17 +7017,21 @@
     <mergeCell ref="B154:F154"/>
     <mergeCell ref="A78:F78"/>
     <mergeCell ref="A65:F65"/>
+    <mergeCell ref="A363:F363"/>
     <mergeCell ref="B156:F156"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="B155:F155"/>
     <mergeCell ref="B264:F264"/>
     <mergeCell ref="B320:F320"/>
+    <mergeCell ref="B391:F391"/>
+    <mergeCell ref="B385:F385"/>
     <mergeCell ref="A302:F302"/>
     <mergeCell ref="B86:F86"/>
     <mergeCell ref="B262:F262"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="B101:F101"/>
     <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A389:F389"/>
     <mergeCell ref="A327:F327"/>
     <mergeCell ref="B182:F182"/>
     <mergeCell ref="A220:F220"/>
@@ -5992,21 +7042,28 @@
     <mergeCell ref="B275:F275"/>
     <mergeCell ref="B340:F340"/>
     <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B404:F404"/>
     <mergeCell ref="B81:F81"/>
     <mergeCell ref="B252:F252"/>
+    <mergeCell ref="B366:F366"/>
     <mergeCell ref="A50:F50"/>
+    <mergeCell ref="B381:F381"/>
     <mergeCell ref="A150:F150"/>
+    <mergeCell ref="A386:F386"/>
     <mergeCell ref="B170:F170"/>
     <mergeCell ref="B157:F157"/>
     <mergeCell ref="B234:F234"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B172:F172"/>
+    <mergeCell ref="B392:F392"/>
     <mergeCell ref="A289:F289"/>
     <mergeCell ref="B186:F186"/>
     <mergeCell ref="B288:F288"/>
     <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B394:F394"/>
     <mergeCell ref="A291:F291"/>
     <mergeCell ref="B265:F265"/>
+    <mergeCell ref="A399:F399"/>
     <mergeCell ref="A305:F305"/>
     <mergeCell ref="A292:F292"/>
     <mergeCell ref="B54:F54"/>
@@ -6016,10 +7073,15 @@
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B341:F341"/>
     <mergeCell ref="B120:F120"/>
+    <mergeCell ref="B405:F405"/>
     <mergeCell ref="B57:F57"/>
     <mergeCell ref="B171:F171"/>
+    <mergeCell ref="B407:F407"/>
     <mergeCell ref="A176:F176"/>
     <mergeCell ref="B9:F9"/>
+    <mergeCell ref="A412:F412"/>
+    <mergeCell ref="A387:F387"/>
+    <mergeCell ref="B359:F359"/>
     <mergeCell ref="B204:F204"/>
     <mergeCell ref="B296:F296"/>
     <mergeCell ref="B173:F173"/>
@@ -6036,6 +7098,7 @@
     <mergeCell ref="A229:F229"/>
     <mergeCell ref="B255:F255"/>
     <mergeCell ref="B226:F226"/>
+    <mergeCell ref="A402:F402"/>
     <mergeCell ref="B192:F192"/>
     <mergeCell ref="B284:F284"/>
     <mergeCell ref="B222:F222"/>
@@ -6046,17 +7109,20 @@
     <mergeCell ref="B110:F110"/>
     <mergeCell ref="B286:F286"/>
     <mergeCell ref="A128:F128"/>
+    <mergeCell ref="A364:F364"/>
     <mergeCell ref="A219:F219"/>
     <mergeCell ref="B297:F297"/>
     <mergeCell ref="B235:F235"/>
     <mergeCell ref="A52:F52"/>
     <mergeCell ref="B103:F103"/>
     <mergeCell ref="B205:F205"/>
+    <mergeCell ref="B403:F403"/>
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B169:F169"/>
     <mergeCell ref="A187:F187"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B194:F194"/>
+    <mergeCell ref="B365:F365"/>
     <mergeCell ref="A118:F118"/>
     <mergeCell ref="A189:F189"/>
     <mergeCell ref="B71:F71"/>
@@ -6070,6 +7136,7 @@
     <mergeCell ref="B60:F60"/>
     <mergeCell ref="B231:F231"/>
     <mergeCell ref="B287:F287"/>
+    <mergeCell ref="B358:F358"/>
     <mergeCell ref="A200:F200"/>
     <mergeCell ref="B84:F84"/>
     <mergeCell ref="A24:F24"/>
@@ -6079,22 +7146,30 @@
     <mergeCell ref="B142:F142"/>
     <mergeCell ref="B80:F80"/>
     <mergeCell ref="B213:F213"/>
+    <mergeCell ref="B384:F384"/>
+    <mergeCell ref="B378:F378"/>
+    <mergeCell ref="A360:F360"/>
     <mergeCell ref="B144:F144"/>
     <mergeCell ref="B242:F242"/>
     <mergeCell ref="A335:F335"/>
     <mergeCell ref="A151:F151"/>
     <mergeCell ref="A126:F126"/>
     <mergeCell ref="A259:F259"/>
+    <mergeCell ref="A424:F424"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="A240:F240"/>
     <mergeCell ref="B318:F318"/>
+    <mergeCell ref="A411:F411"/>
     <mergeCell ref="A190:F190"/>
     <mergeCell ref="B333:F333"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B308:F308"/>
     <mergeCell ref="B99:F99"/>
+    <mergeCell ref="B422:F422"/>
+    <mergeCell ref="B397:F397"/>
     <mergeCell ref="B74:F74"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B372:F372"/>
     <mergeCell ref="B310:F310"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A79:F79"/>
@@ -6109,7 +7184,9 @@
     <mergeCell ref="B152:F152"/>
     <mergeCell ref="B323:F323"/>
     <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A374:F374"/>
     <mergeCell ref="B244:F244"/>
+    <mergeCell ref="A361:F361"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="B145:F145"/>
     <mergeCell ref="A140:F140"/>
@@ -6119,15 +7196,19 @@
     <mergeCell ref="B147:F147"/>
     <mergeCell ref="B245:F245"/>
     <mergeCell ref="A279:F279"/>
+    <mergeCell ref="A350:F350"/>
     <mergeCell ref="A94:F94"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B334:F334"/>
     <mergeCell ref="B309:F309"/>
     <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B380:F380"/>
     <mergeCell ref="A316:F316"/>
     <mergeCell ref="B100:F100"/>
     <mergeCell ref="B311:F311"/>
     <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B382:F382"/>
+    <mergeCell ref="A376:F376"/>
     <mergeCell ref="B102:F102"/>
     <mergeCell ref="A209:F209"/>
     <mergeCell ref="B29:F29"/>
@@ -6136,11 +7217,13 @@
     <mergeCell ref="B95:F95"/>
     <mergeCell ref="B266:F266"/>
     <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B393:F393"/>
     <mergeCell ref="B331:F331"/>
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B330:F330"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B395:F395"/>
     <mergeCell ref="A66:F66"/>
     <mergeCell ref="B261:F261"/>
     <mergeCell ref="B184:F184"/>
@@ -6150,11 +7233,15 @@
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="B166:F166"/>
+    <mergeCell ref="B408:F408"/>
     <mergeCell ref="A161:F161"/>
+    <mergeCell ref="B352:F352"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B174:F174"/>
     <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B423:F423"/>
     <mergeCell ref="B168:F168"/>
+    <mergeCell ref="B410:F410"/>
     <mergeCell ref="B143:F143"/>
     <mergeCell ref="B281:F281"/>
     <mergeCell ref="B20:F20"/>
@@ -6163,16 +7250,22 @@
     <mergeCell ref="A237:F237"/>
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A277:F277"/>
+    <mergeCell ref="B355:F355"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="B121:F121"/>
+    <mergeCell ref="B357:F357"/>
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B167:F167"/>
     <mergeCell ref="B332:F332"/>
     <mergeCell ref="B111:F111"/>
+    <mergeCell ref="B421:F421"/>
     <mergeCell ref="B98:F98"/>
+    <mergeCell ref="B396:F396"/>
     <mergeCell ref="B175:F175"/>
     <mergeCell ref="A230:F230"/>
+    <mergeCell ref="A401:F401"/>
+    <mergeCell ref="B398:F398"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A304:F304"/>
     <mergeCell ref="B124:F124"/>
@@ -6185,25 +7278,32 @@
     <mergeCell ref="B109:F109"/>
     <mergeCell ref="A177:F177"/>
     <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B351:F351"/>
     <mergeCell ref="B345:F345"/>
     <mergeCell ref="A164:F164"/>
+    <mergeCell ref="B416:F416"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B193:F193"/>
     <mergeCell ref="B295:F295"/>
     <mergeCell ref="B46:F46"/>
     <mergeCell ref="B282:F282"/>
     <mergeCell ref="A179:F179"/>
+    <mergeCell ref="B409:F409"/>
     <mergeCell ref="B48:F48"/>
     <mergeCell ref="A116:F116"/>
+    <mergeCell ref="A414:F414"/>
     <mergeCell ref="A53:F53"/>
     <mergeCell ref="A324:F324"/>
     <mergeCell ref="A180:F180"/>
     <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B371:F371"/>
     <mergeCell ref="A93:F93"/>
+    <mergeCell ref="B379:F379"/>
     <mergeCell ref="A328:F328"/>
     <mergeCell ref="B300:F300"/>
     <mergeCell ref="B183:F183"/>
     <mergeCell ref="B201:F201"/>
+    <mergeCell ref="B406:F406"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B212:F212"/>
     <mergeCell ref="B206:F206"/>
@@ -6213,14 +7313,19 @@
     <mergeCell ref="A247:F247"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A312:F312"/>
+    <mergeCell ref="B353:F353"/>
     <mergeCell ref="A106:F106"/>
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B417:F417"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B196:F196"/>
+    <mergeCell ref="B367:F367"/>
     <mergeCell ref="B112:F112"/>
     <mergeCell ref="B283:F283"/>
+    <mergeCell ref="B354:F354"/>
+    <mergeCell ref="B419:F419"/>
     <mergeCell ref="B298:F298"/>
     <mergeCell ref="B285:F285"/>
     <mergeCell ref="A325:F325"/>
